--- a/public/templates/equiwings-rider-import-template.xlsx
+++ b/public/templates/equiwings-rider-import-template.xlsx
@@ -24630,7 +24630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B39"/>
+  <dimension ref="B2:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -24695,181 +24695,195 @@
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2.  File → Save As → CSV (Comma delimited) (.csv).  The upload page takes CSV, not .xlsx.</t>
+          <t>2.  In Equiwings: Riders → Bulk Upload Riders, and choose this .xlsx file directly.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>3.  In Equiwings: Riders → Import, choose the CSV, and press Preview first.</t>
+          <t xml:space="preserve">    Do NOT Save As → CSV first. Excel rewrites dates on CSV export (2014-08-23 comes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>4.  Preview reports duplicates and bad rows WITHOUT saving anything. Fix, then Import.</t>
+          <t xml:space="preserve">    back as 23-08-2014) and every one of those rows is then rejected.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>3.  Press Preview first. It reports duplicates and bad rows WITHOUT saving anything.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>4.  Fix the rows it names, then press Import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Dates and mobile numbers — the one thing that trips people up</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Type dates as plain text in the form 2014-08-23. If Excel converts a cell to its own</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>date format, the CSV can come out as 23-08-2014 and every one of those rows will be</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>rejected. The columns in this file are pre-set to Text to prevent that — if you paste</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="5" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>from elsewhere, use Paste Special → Values.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Duplicates</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>A rider already on the system with the same mobile number is skipped, not duplicated.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>The same mobile appearing twice inside the file is reported as an error.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Example rows (do not paste these in — they are here so the sheet stays clean)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>first_name  last_name  mobile      dob         parent_email        gender  school       joining_date  level</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Aarav       Sharma     9876543210  2014-08-23  priya@family.in     male    DPS Noida    2026-04-01</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Diya        Kapoor     9812345678  2016-01-09  raj@family.in       female               2026-04-01    2</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Batches are NOT in this sheet</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Assign riders to a batch after uploading, from the Riders page — select several and</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>assign in one action. A class name typed here had to match ours character for</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>character, which made it the most error-prone cell in the file.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>What happens after you upload</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Riders are created but HELD — they cannot be put on a register until the indemnity</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>and injury NOC are signed. Send the signing link from Riders &gt; Consent Collection;</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>each rider goes active automatically once their parent signs. That link needs an</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>email address, which is why parent_email is the most important optional column.</t>
         </is>

--- a/public/templates/equiwings-rider-import-template.xlsx
+++ b/public/templates/equiwings-rider-import-template.xlsx
@@ -512,7 +512,7 @@
           <t>last_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
@@ -547,12 +547,12 @@
           <t>gender</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>emergency_name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>emergency_phone</t>
         </is>
@@ -587,17 +587,17 @@
           <t>allergies</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>school</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>school_class</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>school_section</t>
         </is>
@@ -24630,7 +24630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B41"/>
+  <dimension ref="B2:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -24778,14 +24778,14 @@
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>A rider already on the system with the same mobile number is skipped, not duplicated.</t>
+          <t>A rider already on the system with the same name, date of birth and mobile is skipped,</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>The same mobile appearing twice inside the file is reported as an error.</t>
+          <t>not duplicated. Mobile is optional — when it's blank, name + date of birth alone is used.</t>
         </is>
       </c>
     </row>
@@ -24802,88 +24802,102 @@
     <row r="28">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>first_name  last_name  mobile      dob         parent_email        gender  school       joining_date  level</t>
+          <t>first_name  last_name  mobile      dob         parent_email        gender  school       school_class  school_section</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Aarav       Sharma     9876543210  2014-08-23  priya@family.in     male    DPS Noida    2026-04-01</t>
+          <t>Aarav       Sharma     9876543210  2014-08-23  priya@family.in     male    DPS Noida    7             A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Diya        Kapoor     9812345678  2016-01-09  raj@family.in       female               2026-04-01    2</t>
+          <t>Diya        Kapoor                2016-01-09  raj@family.in       female  DPS Noida    5             B</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Diya has no mobile of her own — that's fine now. school / school_class / school_section are the</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>three that must always be filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Batches are NOT in this sheet</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Assign riders to a batch after uploading, from the Riders page — select several and</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>assign in one action. A class name typed here had to match ours character for</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>character, which made it the most error-prone cell in the file.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>What happens after you upload</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Riders are created but HELD — they cannot be put on a register until the indemnity</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>and injury NOC are signed. Send the signing link from Riders &gt; Consent Collection;</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="5" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>each rider goes active automatically once their parent signs. That link needs an</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>email address, which is why parent_email is the most important optional column.</t>
         </is>
